--- a/output_tcc_var_selic_ativ_espec_Modelo8_subamostras/2015_2026/tabelas/johansen_Oleo_diesel_IPCA_Brasil.xlsx
+++ b/output_tcc_var_selic_ativ_espec_Modelo8_subamostras/2015_2026/tabelas/johansen_Oleo_diesel_IPCA_Brasil.xlsx
@@ -440,7 +440,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>163.191506602361</v>
+        <v>163.1915066023618</v>
       </c>
       <c r="B2" t="n">
         <v>120.3673</v>
@@ -454,7 +454,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>92.90382742796093</v>
+        <v>92.90382742796091</v>
       </c>
       <c r="B3" t="n">
         <v>91.10899999999999</v>
@@ -468,7 +468,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>61.06131632770313</v>
+        <v>61.06131632770327</v>
       </c>
       <c r="B4" t="n">
         <v>65.8202</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>34.45653054928427</v>
+        <v>34.4565305492842</v>
       </c>
       <c r="B5" t="n">
         <v>44.4929</v>
@@ -496,7 +496,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>21.00850223188263</v>
+        <v>21.00850223188257</v>
       </c>
       <c r="B6" t="n">
         <v>27.0669</v>
@@ -510,7 +510,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>10.46155557693253</v>
+        <v>10.46155557693254</v>
       </c>
       <c r="B7" t="n">
         <v>13.4294</v>
@@ -524,7 +524,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2.110429601465576</v>
+        <v>2.110429601465704</v>
       </c>
       <c r="B8" t="n">
         <v>2.7055</v>
